--- a/master/result/58_重生校园_逆袭学霸之路/58_重生校园_逆袭学霸之路.xlsx
+++ b/master/result/58_重生校园_逆袭学霸之路/58_重生校园_逆袭学霸之路.xlsx
@@ -397,522 +397,661 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:D46"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sand</v>
       </c>
       <c r="B2" t="str">
-        <v>sand</v>
+        <v>/sand/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>沙</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>minority</v>
       </c>
       <c r="B3" t="str">
-        <v>minority</v>
+        <v>/minority/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>少数</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>talk</v>
       </c>
       <c r="B4" t="str">
-        <v>talk</v>
+        <v>/tɔːk/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>谈话</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>shelf</v>
       </c>
       <c r="B5" t="str">
-        <v>shelf</v>
+        <v>/shelf/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>架子</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>blackboard</v>
       </c>
       <c r="B6" t="str">
-        <v>blackboard</v>
+        <v>/blackboard/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>黑板</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>relativity</v>
       </c>
       <c r="B7" t="str">
-        <v>relativity</v>
+        <v>/relativity/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>相对论</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>concentrate</v>
       </c>
       <c r="B8" t="str">
-        <v>concentrate</v>
+        <v>/ˈkɒnsntreɪt/</v>
       </c>
       <c r="C8" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>集中</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>hardly</v>
       </c>
       <c r="B9" t="str">
-        <v>hardly</v>
+        <v>/hardly/</v>
       </c>
       <c r="C9" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D9" t="str">
         <v>几乎不</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>strain</v>
       </c>
       <c r="B10" t="str">
-        <v>strain</v>
+        <v>/strain/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>努力</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>velocity</v>
       </c>
       <c r="B11" t="str">
-        <v>velocity</v>
+        <v>/velocity/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>速度</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>scream</v>
       </c>
       <c r="B12" t="str">
-        <v>scream</v>
+        <v>/scream/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>尖叫</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>soda</v>
       </c>
       <c r="B13" t="str">
-        <v>soda</v>
+        <v>/soda/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>汽水</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>inspiration</v>
       </c>
       <c r="B14" t="str">
-        <v>inspiration</v>
+        <v>/inspiration/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>灵感</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>if</v>
       </c>
       <c r="B15" t="str">
-        <v>if</v>
+        <v>/if/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>如果</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>somewhat</v>
       </c>
       <c r="B16" t="str">
-        <v>somewhat</v>
+        <v>/somewhat/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>稍微</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>strenuous</v>
       </c>
       <c r="B17" t="str">
-        <v>strenuous</v>
+        <v>/strenuous/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>费力的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>status</v>
       </c>
       <c r="B18" t="str">
-        <v>status</v>
+        <v>/status/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>地位</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>clever</v>
       </c>
       <c r="B19" t="str">
-        <v>clever</v>
+        <v>/ˈklevə/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>聪明</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>embarrass</v>
       </c>
       <c r="B20" t="str">
-        <v>embarrass</v>
+        <v>/ɪmˈbærəs/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>尴尬</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>innovation</v>
       </c>
       <c r="B21" t="str">
-        <v>innovation</v>
+        <v>/innovation/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>创新</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>sniff</v>
       </c>
       <c r="B22" t="str">
-        <v>sniff</v>
+        <v>/sniff/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>轻哼</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>analogy</v>
       </c>
       <c r="B23" t="str">
-        <v>analogy</v>
+        <v>/analogy/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>类比</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>logical</v>
       </c>
       <c r="B24" t="str">
-        <v>logical</v>
+        <v>/logical/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>逻辑</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>supreme</v>
       </c>
       <c r="B25" t="str">
-        <v>supreme</v>
+        <v>/supreme/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>最高</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>caution</v>
       </c>
       <c r="B26" t="str">
-        <v>caution</v>
+        <v>/caution/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>谨慎</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>perpetual</v>
       </c>
       <c r="B27" t="str">
-        <v>perpetual</v>
+        <v>/perpetual/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>永久</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>obsolete</v>
       </c>
       <c r="B28" t="str">
-        <v>obsolete</v>
+        <v>/obsolete/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>过时的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>kettle</v>
       </c>
       <c r="B29" t="str">
-        <v>kettle</v>
+        <v>/kettle/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>水壶</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>pet</v>
       </c>
       <c r="B30" t="str">
-        <v>pet</v>
+        <v>/pet/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>宠物</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>spring</v>
       </c>
       <c r="B31" t="str">
-        <v>spring</v>
+        <v>/sprɪŋ/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>春天</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>rhythm</v>
       </c>
       <c r="B32" t="str">
-        <v>rhythm</v>
+        <v>/rhythm/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>节奏</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>ahead</v>
       </c>
       <c r="B33" t="str">
-        <v>ahead</v>
+        <v>/ahead/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>向前</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>body</v>
       </c>
       <c r="B34" t="str">
-        <v>body</v>
+        <v>/body/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>身体</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>government</v>
       </c>
       <c r="B35" t="str">
-        <v>government</v>
+        <v>/government/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>政府</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>prospective</v>
       </c>
       <c r="B36" t="str">
-        <v>prospective</v>
+        <v>/prospective/</v>
       </c>
       <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
         <v>预期的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>fixture</v>
       </c>
       <c r="B37" t="str">
-        <v>fixture</v>
+        <v>/fixture/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>固定设备</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>football</v>
       </c>
       <c r="B38" t="str">
-        <v>football</v>
+        <v>/football/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>足球</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>cope</v>
       </c>
       <c r="B39" t="str">
-        <v>cope</v>
+        <v>/kəʊp/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>应对</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>hostile</v>
       </c>
       <c r="B40" t="str">
-        <v>hostile</v>
+        <v>/hostile/</v>
       </c>
       <c r="C40" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D40" t="str">
         <v>敌对的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>brake</v>
       </c>
       <c r="B41" t="str">
-        <v>brake</v>
+        <v>/breɪk/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>刹车</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>grim</v>
       </c>
       <c r="B42" t="str">
-        <v>grim</v>
+        <v>/grim/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>严酷</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>fatal</v>
       </c>
       <c r="B43" t="str">
-        <v>fatal</v>
+        <v>/fatal/</v>
       </c>
       <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
         <v>致命的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>derive</v>
       </c>
       <c r="B44" t="str">
-        <v>derive</v>
+        <v>/derive/</v>
       </c>
       <c r="C44" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D44" t="str">
         <v>获得</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>therefore</v>
       </c>
       <c r="B45" t="str">
-        <v>therefore</v>
+        <v>/therefore/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>因此</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>prime</v>
       </c>
       <c r="B46" t="str">
-        <v>prime</v>
+        <v>/prime/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>全盛期</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
   </ignoredErrors>
 </worksheet>
 </file>